--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -856,13 +856,7 @@
     <t>0..1 to account for primarily narrative only resources.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Identification of the condition or diagnosis.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://minsal.cl/listaespera/ValueSet/VSTipoCodDiagnostica</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -916,9 +910,6 @@
     <t>Condition.code.coding.code</t>
   </si>
   <si>
-    <t>http://minsal.cl/listaespera/ValueSet/VSTipoCodDiagnostica</t>
-  </si>
-  <si>
     <t>Condition.code.coding.display</t>
   </si>
   <si>
@@ -938,6 +929,9 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Condition.code. If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).  May be a summary code, or a reference to a very precise definition of the location, or both.</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -4780,13 +4774,11 @@
         <v>75</v>
       </c>
       <c r="W27" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="X27" s="2"/>
+      <c r="Y27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>75</v>
@@ -4819,27 +4811,27 @@
         <v>97</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4954,7 +4946,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
@@ -5071,7 +5063,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5190,7 +5182,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5305,7 +5297,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
@@ -5422,7 +5414,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5541,7 +5533,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5658,7 +5650,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5716,11 +5708,13 @@
         <v>75</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="X35" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Y35" t="s" s="2">
-        <v>288</v>
+        <v>75</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>75</v>
@@ -5773,7 +5767,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5890,7 +5884,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -6009,7 +6003,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6128,7 +6122,7 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6154,13 +6148,13 @@
         <v>152</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
@@ -6186,13 +6180,13 @@
         <v>75</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>75</v>
@@ -6210,7 +6204,7 @@
         <v>75</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>76</v>
@@ -6228,28 +6222,28 @@
         <v>75</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" t="s" s="2">
@@ -6268,17 +6262,17 @@
         <v>86</v>
       </c>
       <c r="J40" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>75</v>
@@ -6327,7 +6321,7 @@
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>85</v>
@@ -6342,19 +6336,19 @@
         <v>97</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AK40" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>75</v>
@@ -6362,7 +6356,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6385,16 +6379,16 @@
         <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="K41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
@@ -6444,7 +6438,7 @@
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>76</v>
@@ -6459,19 +6453,19 @@
         <v>97</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AK41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>75</v>
@@ -6479,7 +6473,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6502,16 +6496,16 @@
         <v>86</v>
       </c>
       <c r="J42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="K42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
@@ -6561,7 +6555,7 @@
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>76</v>
@@ -6576,19 +6570,19 @@
         <v>97</v>
       </c>
       <c r="AJ42" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>75</v>
@@ -6596,7 +6590,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6619,16 +6613,16 @@
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
@@ -6678,7 +6672,7 @@
         <v>75</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>76</v>
@@ -6687,7 +6681,7 @@
         <v>85</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>97</v>
@@ -6702,10 +6696,10 @@
         <v>75</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>75</v>
@@ -6713,7 +6707,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6736,13 +6730,13 @@
         <v>86</v>
       </c>
       <c r="J44" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6793,7 +6787,7 @@
         <v>75</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>76</v>
@@ -6814,13 +6808,13 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>75</v>
@@ -6828,7 +6822,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6851,13 +6845,13 @@
         <v>86</v>
       </c>
       <c r="J45" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>346</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6908,7 +6902,7 @@
         <v>75</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>76</v>
@@ -6932,10 +6926,10 @@
         <v>75</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>75</v>
@@ -6943,7 +6937,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6966,13 +6960,13 @@
         <v>86</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7023,7 +7017,7 @@
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7044,13 +7038,13 @@
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>75</v>
@@ -7058,7 +7052,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7081,13 +7075,13 @@
         <v>75</v>
       </c>
       <c r="J47" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7138,7 +7132,7 @@
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7150,7 +7144,7 @@
         <v>75</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>75</v>
@@ -7162,7 +7156,7 @@
         <v>75</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7173,7 +7167,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7288,7 +7282,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7405,11 +7399,11 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" t="s" s="2">
@@ -7431,10 +7425,10 @@
         <v>131</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
         <v>134</v>
@@ -7489,7 +7483,7 @@
         <v>75</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>76</v>
@@ -7524,7 +7518,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7550,10 +7544,10 @@
         <v>152</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7580,13 +7574,13 @@
         <v>75</v>
       </c>
       <c r="W51" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="Z51" t="s" s="2">
         <v>75</v>
@@ -7604,7 +7598,7 @@
         <v>75</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>76</v>
@@ -7613,7 +7607,7 @@
         <v>85</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>97</v>
@@ -7622,13 +7616,13 @@
         <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7639,7 +7633,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7662,13 +7656,13 @@
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7719,7 +7713,7 @@
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>76</v>
@@ -7728,7 +7722,7 @@
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>97</v>
@@ -7743,7 +7737,7 @@
         <v>75</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>75</v>
@@ -7754,7 +7748,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7780,10 +7774,10 @@
         <v>152</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -7810,13 +7804,13 @@
         <v>75</v>
       </c>
       <c r="W53" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="Z53" t="s" s="2">
         <v>75</v>
@@ -7834,7 +7828,7 @@
         <v>75</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -7858,7 +7852,7 @@
         <v>75</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>75</v>
@@ -7869,7 +7863,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -7892,16 +7886,16 @@
         <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -7951,7 +7945,7 @@
         <v>75</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
@@ -7963,7 +7957,7 @@
         <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>75</v>
@@ -7975,7 +7969,7 @@
         <v>75</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -7986,7 +7980,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
@@ -8101,7 +8095,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8218,11 +8212,11 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" t="s" s="2">
@@ -8244,10 +8238,10 @@
         <v>131</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>134</v>
@@ -8302,7 +8296,7 @@
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8337,7 +8331,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8363,10 +8357,10 @@
         <v>152</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8393,13 +8387,13 @@
         <v>75</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="Z58" t="s" s="2">
         <v>75</v>
@@ -8417,7 +8411,7 @@
         <v>75</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>76</v>
@@ -8426,13 +8420,13 @@
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>252</v>
@@ -8441,10 +8435,10 @@
         <v>75</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>75</v>
@@ -8452,7 +8446,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8475,13 +8469,13 @@
         <v>86</v>
       </c>
       <c r="J59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8532,7 +8526,7 @@
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>76</v>
@@ -8541,7 +8535,7 @@
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>97</v>
@@ -8556,10 +8550,10 @@
         <v>75</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>75</v>
@@ -8567,7 +8561,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8590,13 +8584,13 @@
         <v>75</v>
       </c>
       <c r="J60" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8647,7 +8641,7 @@
         <v>75</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>76</v>
@@ -8662,16 +8656,16 @@
         <v>97</v>
       </c>
       <c r="AJ60" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
+++ b/refs/heads/master/StructureDefinition-CondicionAtenderDiagnosticoConfirmacionLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
